--- a/复采名单.xlsx
+++ b/复采名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,11 +482,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>478</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+          <t>Loccitane欧舒丹 玫瑰护手霜30ml新版</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16</v>
+        <v>489</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NARS 遮瑕膏 VANILLA色号</t>
+          <t>SK2光韵清透CC霜绿色50g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -526,11 +526,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>490</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NARS空气唇釉686 lose control</t>
+          <t>SK2光韵清透全效防晒透明色50g</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -548,11 +548,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>38</v>
+        <v>511</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TF汤姆福特 乌木沉香 100ml</t>
+          <t>黛珂四色散粉101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -570,11 +570,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YSL自由之水浓香90ml</t>
+          <t>迪奥 花漾甜心香体喷雾100ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -592,11 +592,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62</v>
+        <v>550</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>阿玛尼权力粉底液3号</t>
+          <t>迪奥 真我EDT 100ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -614,11 +614,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68</v>
+        <v>560</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>芭比波朗月光石眼影</t>
+          <t>范思哲 粉钻女士EDT30ml对装</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,11 +636,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黛珂AQ舒活滋润化妆水200ml</t>
+          <t>馥蕾诗睡莲焕肤水150ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,11 +658,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106</v>
+        <v>627</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>赫莲娜 黑绷带50ml</t>
+          <t>资生堂悦薇眼膜12片/盒（新款）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -680,16 +680,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107</v>
+        <v>632</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>赫莲娜黑绷带100ml</t>
+          <t>Estee Lauder 雅诗兰黛 抗蓝光眼霜15ml*2（第五代）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -700,622 +700,6 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>198</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>229</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>262</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>欧舒丹玫瑰身体乳250ml</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>279</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>兰蔻菁纯眼霜20ml两瓶装</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>291</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>293</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">阿玛尼权力PR0粉底1.5 30ml </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>320</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>后拱辰享美黄金气垫13G+替换装13G</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>325</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>纪梵希粉丝绒N37</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>339</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>雅诗兰黛白金粉底液1CO</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>345</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>362</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SK2大红瓶清爽版80g</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>365</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SK-II 小银瓶精华50ML</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>380</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MAC 无暇粉底液NC12 30ML</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>401</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>植村秀绿茶卸妆油150ml</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>421</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>伊丽莎白雅顿经典润泽护唇膏 SPF15 3.7g</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>442</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NARS 水光绚色液体腮红 Secret Lover 7ml</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NARS 超方瓶粉底液#L1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SK2大红瓶滋润面霜100g</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>82</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>黛珂沁活晶澈润肤精华水200ml</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>123</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>纪梵希 小粉皮口红#N333</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>138</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>科颜氏 金盏花植物精华化妆水500ml</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>146</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>拉夫劳伦地球淡香氛 40ml</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>190</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>191</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>250</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CK Man男士香水 50ml EDT</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>294</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>兰蔻小黑瓶眼霜20ml</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>356</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>YSL圣罗兰黑金方管13色</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>358</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>YSL圣罗兰黑金方管1968</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>已采集</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/复采名单.xlsx
+++ b/复采名单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,11 +482,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>478</v>
+        <v>62</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Loccitane欧舒丹 玫瑰护手霜30ml新版</t>
+          <t>阿玛尼权力粉底液3号</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,16 +504,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>489</v>
+        <v>72</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SK2光韵清透CC霜绿色50g</t>
+          <t>黛珂 防晒防水版60g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -526,16 +526,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>490</v>
+        <v>76</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SK2光韵清透全效防晒透明色50g</t>
+          <t>黛珂AQ白檀水200ml清爽型</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,16 +548,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>511</v>
+        <v>78</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黛珂四色散粉101</t>
+          <t>黛珂AQ舒活滋润化妆水200ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -570,16 +570,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>522</v>
+        <v>85</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>迪奥 花漾甜心香体喷雾100ml</t>
+          <t>黛珂紫苏水 300ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -592,16 +592,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>550</v>
+        <v>106</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>迪奥 真我EDT 100ml</t>
+          <t>赫莲娜 黑绷带50ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -614,16 +614,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>560</v>
+        <v>151</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>范思哲 粉钻女士EDT30ml对装</t>
+          <t>兰蔻粉水400ml 旧版</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -636,16 +636,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>571</v>
+        <v>155</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>馥蕾诗睡莲焕肤水150ml</t>
+          <t>兰蔻极光美白精华50ml 新款</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,16 +658,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>627</v>
+        <v>237</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>资生堂悦薇眼膜12片/盒（新款）</t>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>已采集</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,11 +680,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>632</v>
+        <v>274</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Estee Lauder 雅诗兰黛 抗蓝光眼霜15ml*2（第五代）</t>
+          <t>苏秘气垫1号</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -700,6 +700,248 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>308</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>314</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>358</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>368</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>431</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 Secret Lover 7ml</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>511</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黛珂四色散粉101</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>522</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>迪奥 花漾甜心香体喷雾100ml</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>536</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>迪奥 旷野男士典藏香精EDP 100ml</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>571</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲焕肤水150ml</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>603</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>香奈儿 嘉柏丽尔香水EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>629</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Burberry 巴宝莉 花与她果漾青提软糖淡香水100ml</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
